--- a/AAII_Financials/Quarterly/TTE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TTE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>TTE</t>
   </si>
@@ -656,371 +656,383 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57097000</v>
+      </c>
+      <c r="E8" s="3">
         <v>49516000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45925000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>43844000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44676000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>47899000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>47115000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>47429000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49183000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51883000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54765000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54413000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>51534000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>58233000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>63953000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>64962000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>70445000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63950000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>55298000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>49070000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41633000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38633000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32348000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27217000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21562000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>38577000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>43385000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>42538000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38308000</v>
+      </c>
+      <c r="E9" s="3">
         <v>27347000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29536000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27191000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29158000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30855000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30342000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31425000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32117000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33780000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>37150000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33676000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33864000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38351000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42755000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41509000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46023000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40762000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>36189000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>32574000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27108000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24289000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20781000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16942000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11842000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26107000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>28126000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>27805000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>18789000</v>
+      </c>
+      <c r="E10" s="3">
         <v>22169000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16389000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16653000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15518000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17044000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16773000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16004000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17066000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18103000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17615000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20737000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17670000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19882000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21198000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23453000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24422000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23188000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19109000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16496000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14525000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14344000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11567000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10275000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9720000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12470000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15259000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14733000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,19 +1063,20 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="3">
         <v>810000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>91</v>
@@ -1071,11 +1084,11 @@
       <c r="H12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="3">
         <v>805000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>91</v>
@@ -1083,11 +1096,11 @@
       <c r="L12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="3">
         <v>774000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>91</v>
@@ -1095,50 +1108,53 @@
       <c r="P12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R12" s="3">
         <v>250000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>71000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>117000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>136000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>323000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>127000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>123000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>167000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>338000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>139000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>114000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>140000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>231000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>96000</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,180 +1239,189 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>1148000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1253000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>286000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>209000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2429000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1107000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>644000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2293000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>614000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>469000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>60000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1681000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>514000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>566000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2116000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>758000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>338000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-301000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-217000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>102000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>421000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8575000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>905000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>832000</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3075000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2058000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3461000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2994000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3049000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2998000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3647000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2285000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2976000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2298000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2385000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2441000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2637000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3002000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2221000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2926000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3038000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3148000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3484000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3172000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3105000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3180000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3172000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3203000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3302000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3635000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3761000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3987000</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1424,180 +1449,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>49795000</v>
+      </c>
+      <c r="E17" s="3">
         <v>39438000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42029000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38368000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40425000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41789000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41729000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41925000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43170000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44124000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47340000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44852000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44835000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49530000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53889000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>51699000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57464000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53719000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47326000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42681000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>36747000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34063000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30864000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25909000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>29895000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>38629000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>39774000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>38925000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>7302000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10078000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3896000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5476000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4251000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6110000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5386000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5504000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6013000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7759000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7425000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9561000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6699000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8703000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10064000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13263000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12981000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10231000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7972000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6389000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4886000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4570000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1484000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1308000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8333000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3611000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3613000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,438 +1660,454 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1899000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1359000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>275000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1538000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1299000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-979000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>927000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-483000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-876000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1867000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1550000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1414000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-623000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1376000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>173000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>195000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1321000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>86000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2037000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1517000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-469000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>955000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>117000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>152000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-138000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>584000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>493000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1366000</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>12276000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13495000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7082000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10008000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8599000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10087000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8106000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8272000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9865000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11924000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8260000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13416000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9959000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13081000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12986000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16490000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14981000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14895000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14231000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11267000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7704000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8998000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5397000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5094000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3230000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4262000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8728000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9221000</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>817000</v>
+      </c>
+      <c r="E22" s="3">
         <v>791000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>209000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>808000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>816000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>725000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>134000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>797000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>725000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>708000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>-7000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>726000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>724000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>710000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>719000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>633000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>572000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>462000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>459000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>462000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>509000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>474000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>549000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>589000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>435000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>567000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>603000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>594000</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>8629000</v>
+      </c>
+      <c r="E23" s="3">
         <v>9720000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4758000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6185000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4852000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6654000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6948000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4540000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6572000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8746000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8376000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10094000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6639000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9702000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9518000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12825000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11088000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9855000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9550000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7444000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3908000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5051000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1052000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>871000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8906000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3501000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4385000</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3154000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3788000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1830000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2423000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2106000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2733000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2929000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2179000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2725000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2942000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3339000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3404000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2487000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4071000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>6077000</v>
       </c>
       <c r="R24" s="3">
         <v>6077000</v>
       </c>
       <c r="S24" s="3">
+        <v>6077000</v>
+      </c>
+      <c r="T24" s="3">
         <v>5284000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4804000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3647000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2692000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1609000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1639000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>149000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>690000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-484000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-37000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>852000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1540000</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2144,180 +2192,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>5475000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5932000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2928000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3762000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2746000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3921000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4019000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2361000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3847000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5804000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5037000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6690000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4152000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5631000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3441000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6748000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5804000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5051000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5903000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4752000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2299000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3412000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>903000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>181000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8422000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2649000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2845000</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>5438000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5810000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2906000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3683000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2687000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3851000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3956000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2294000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3787000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5721000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5063000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6676000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4088000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5557000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3188000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6554000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5605000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4848000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5747000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4551000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2112000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3254000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>810000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>118000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8440000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2527000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2727000</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2402,8 +2459,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2488,8 +2548,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2574,8 +2637,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,180 +2726,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>1899000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1359000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-275000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1538000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1299000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>979000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-927000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>483000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>876000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1867000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1550000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1414000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>623000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1376000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-173000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-195000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1321000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-86000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2037000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1517000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>469000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-955000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-117000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>138000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-584000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-493000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1366000</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>5438000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5810000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2906000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3683000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2687000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3851000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3956000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2294000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3787000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5721000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5063000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6676000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4088000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5557000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3188000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6554000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5605000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4848000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5747000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4551000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2112000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3254000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>810000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>118000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8440000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2527000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2727000</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2918,185 +2993,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>5438000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5810000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2906000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3683000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2687000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3851000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3956000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2294000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3787000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5721000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5063000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6676000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4088000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5557000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3188000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6554000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5605000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4848000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5747000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4551000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2112000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3254000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>810000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>118000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8440000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2527000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2727000</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3127,8 +3211,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3159,782 +3244,810 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>27678000</v>
+      </c>
+      <c r="E41" s="3">
         <v>25693000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26202000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23415000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20424000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22837000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25844000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25672000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23211000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25640000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27263000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24731000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25572000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27985000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>33026000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35941000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>32848000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31276000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21342000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28971000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28643000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30285000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31268000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30593000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>29727000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21634000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27352000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27454000</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>4039000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4173000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3012000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4884000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5183000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6237000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6507000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6151000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6823000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6319000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6165000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6892000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6725000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7535000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8746000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11688000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7863000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7415000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12315000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3910000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4404000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4605000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4630000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6011000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>6570000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7016000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3992000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3781000</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>21184000</v>
+      </c>
+      <c r="E43" s="3">
         <v>22977000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>36870000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19735000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21254000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24882000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40794000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18777000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20647000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24198000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42801000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23598000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22163000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24128000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24378000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28191000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>30796000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32000000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21983000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19865000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17192000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17532000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14068000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12893000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>13481000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>18029000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>18488000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>18568000</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>21373000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23932000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16663000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17058000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17275000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19037000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18868000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18532000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20189000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>20229000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19317000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22512000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18785000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22786000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22936000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>24420000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28542000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>24456000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19952000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19601000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>19162000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16192000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>14730000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12373000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>12688000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11556000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17132000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16226000</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>30991000</v>
+      </c>
+      <c r="E45" s="3">
         <v>35437000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4462000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25842000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26710000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24134000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2077000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24763000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20926000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21140000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2252000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30908000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31552000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28821000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>36638000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>73802000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>55866000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51832000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>35544000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40600000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>18041000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14700000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14983000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15727000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17576000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19850000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>18301000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>15343000</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>105265000</v>
+      </c>
+      <c r="E46" s="3">
         <v>112212000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>89469000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>90934000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>90846000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97127000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96571000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>93895000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>91796000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>97526000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>99529000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108641000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>104797000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>111255000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>125724000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>174042000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>155915000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>146979000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>111136000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>112947000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>87442000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>83314000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>79679000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>77597000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>80042000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>78085000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>85265000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>81372000</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>41220000</v>
+        <v>46762000</v>
       </c>
       <c r="E47" s="3">
+        <v>44097000</v>
+      </c>
+      <c r="F47" s="3">
         <v>42462000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41440000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41524000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39778000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>37829000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38197000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>34540000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33151000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33722000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31495000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31615000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31206000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31671000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32233000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31205000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>32314000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>35082000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>34954000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>35737000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>36489000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>34764000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>32363000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>31528000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>29791000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>29812000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>29677000</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>117889000</v>
+      </c>
+      <c r="E48" s="3">
         <v>116240000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>114694000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>115198000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>116153000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>112249000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>109095000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>110125000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109403000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109462000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>108916000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>106721000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>104174000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107499000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>107101000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>99700000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>101454000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>104450000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>106559000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>105902000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>106791000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>106859000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>108335000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>104355000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>104925000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>113254000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>116408000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>116900000</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>35631000</v>
+      </c>
+      <c r="E49" s="3">
         <v>36387000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37345000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>37764000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36687000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34543000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34238000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33891000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33477000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>33193000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>33083000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>32911000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>31717000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>33234000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31931000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>36376000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>37020000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>32504000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>32484000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>32895000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>33359000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>33239000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>33528000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>33145000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>33114000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>32823000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>33178000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>31539000</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4019,8 +4132,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4105,94 +4221,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>5517000</v>
+        <v>5275000</v>
       </c>
       <c r="E52" s="3">
+        <v>2640000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1486000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2990000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4057000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4000000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2377000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4170000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6704000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6636000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2764000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6701000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5067000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5066000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7437000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7364000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7812000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8332000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8197000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8982000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9378000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9257000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9826000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9522000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9796000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9231000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8631000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7953000</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4277,94 +4399,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>313761000</v>
+      </c>
+      <c r="E54" s="3">
         <v>314562000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>291055000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>291959000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>292817000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>291057000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>285487000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>284005000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>279488000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>283133000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>283654000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>290004000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>281019000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293032000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>303864000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>349715000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>333406000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>324579000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>293458000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>295680000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>272707000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>269158000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>266132000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>256982000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>259405000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>263184000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>273294000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>267441000</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4395,8 +4523,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4427,524 +4556,543 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>41438000</v>
+      </c>
+      <c r="E57" s="3">
         <v>42693000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38065000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38062000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39288000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>42554000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39932000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34668000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36449000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37647000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41335000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37268000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32853000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36037000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>93621000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>129410000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>112198000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>103841000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>79637000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>79625000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57588000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>49025000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>46039000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41686000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>43988000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>47225000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>54143000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>50965000</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>13392000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12825000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12426000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14388000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15498000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14031000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10688000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14341000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11732000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18454000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10036000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17291000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15985000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18164000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15502000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16923000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>16003000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18252000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15035000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>16471000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16983000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>20471000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17099000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>14980000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>16154000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18521000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>14819000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14631000</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>44376000</v>
+      </c>
+      <c r="E59" s="3">
         <v>48724000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27502000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37375000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36430000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33876000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21621000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36700000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34179000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33056000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20624000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39872000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40898000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43062000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>655000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>895000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>457000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>545000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>430000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>813000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>612000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>512000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>991000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>739000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>934000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1282000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>99206000</v>
+      </c>
+      <c r="E60" s="3">
         <v>104242000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92563000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>89825000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91216000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90461000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>87960000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85709000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82360000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>89157000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88785000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>94431000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>89736000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>97263000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>109778000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>147228000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>128658000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>122638000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>95102000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>96909000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>75183000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>70008000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>64676000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>57657000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>60881000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>66680000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>70244000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>66696000</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>49525000</v>
+      </c>
+      <c r="E61" s="3">
         <v>51426000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48995000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>49552000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47584000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45858000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43533000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45750000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42526000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>38053000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40478000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41022000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40427000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42915000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45264000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>44899000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46868000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46546000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49512000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>50810000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>52331000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>52541000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>60203000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>61477000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>61540000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>48896000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>47773000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>47923000</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>18734000</v>
+      </c>
+      <c r="E62" s="3">
         <v>18693000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17322000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20096000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20312000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>19872000</v>
       </c>
       <c r="I62" s="3">
         <v>19872000</v>
       </c>
       <c r="J62" s="3">
+        <v>19872000</v>
+      </c>
+      <c r="K62" s="3">
         <v>20290000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20295000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20961000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21257000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22657000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21295000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21270000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34252000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>36916000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37883000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>35540000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33845000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>34734000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>34617000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>34924000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>35168000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>33437000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33445000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>33174000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>35972000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>35509000</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5029,8 +5177,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5115,8 +5266,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,94 +5355,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>182808000</v>
+      </c>
+      <c r="E66" s="3">
         <v>189325000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>173532000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>174294000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>173815000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>170636000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>165232000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>165389000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>159461000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>161990000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>164201000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>171580000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164567000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>174588000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>192140000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>231894000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>216718000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>208099000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>181722000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>185664000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>164611000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>159863000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>162430000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>154748000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>158200000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>151178000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>156516000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>152447000</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5319,8 +5479,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5405,8 +5566,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5491,8 +5655,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5577,8 +5744,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -5663,19 +5833,22 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" s="3">
         <v>113607000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
@@ -5683,11 +5856,11 @@
       <c r="H72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J72" s="3">
         <v>112151000</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>91</v>
@@ -5695,11 +5868,11 @@
       <c r="L72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N72" s="3">
         <v>102472000</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>91</v>
@@ -5707,8 +5880,8 @@
       <c r="P72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -5749,8 +5922,11 @@
       <c r="AD72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -5835,8 +6011,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -5921,8 +6100,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6007,94 +6189,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>128408000</v>
+      </c>
+      <c r="E76" s="3">
         <v>122541000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>114883000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>115281000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>116642000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>117956000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>117858000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116059000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>117379000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118409000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>116753000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>115767000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>113682000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>115581000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>111724000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>117821000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>116688000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>116480000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>111736000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>110016000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>108096000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>109295000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>103702000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>102234000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>101205000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>112006000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>116778000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>114994000</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6179,185 +6367,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>5438000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5810000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2906000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3683000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2687000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3851000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3956000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2294000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3787000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5721000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5063000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6676000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4088000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5557000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3188000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6554000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5605000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4848000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5747000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4551000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2112000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3254000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>810000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>118000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8440000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2527000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2727000</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6388,94 +6585,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3055000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3003000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3514000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2913000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2993000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2300000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3343000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2919000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2634000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3028000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13685000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-181000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3163000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3216000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2749000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3032000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3321000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4578000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4222000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3361000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3287000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3473000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3796000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3634000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11701000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3730000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4624000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4242000</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6560,8 +6761,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -6646,8 +6850,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -6732,8 +6939,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -6818,8 +7028,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -6904,94 +7117,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>10858000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3361000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10471000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8349000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5960000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2563000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12507000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7171000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9007000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2169000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16150000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9496000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9900000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5133000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5618000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17848000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16284000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7617000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11621000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5640000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7551000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5598000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5674000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4351000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3479000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6599000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8206000</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7022,94 +7241,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-4232000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4621000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2956000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3812000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4766000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2242000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4110000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3420000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3832000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3808000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3870000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4968000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4097000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2986000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5150000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3457000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4540000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2718000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2675000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2410000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3834000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2157000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2409000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4015000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2210000</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7194,8 +7417,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7280,94 +7506,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-3276000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4312000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3434000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3203000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6689000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4805000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3745000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5562000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4558000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3467000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-632000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4987000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4473000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6362000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3681000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4075000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4982000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2378000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3912000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2456000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3104000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4184000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4476000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1901000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2928000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3774000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3925000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6831000</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -7398,94 +7630,98 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>2134000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2277000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2282000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2242000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1921000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1979000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2080000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1986000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1903000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2062000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1923000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1984000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1922000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2002000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4356000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1825000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1928000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1991000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2053000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2094000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2090000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2053000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-825000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1928000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1882000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1876000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -7570,8 +7806,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -7656,8 +7895,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -7742,262 +7984,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-5268000</v>
+      </c>
+      <c r="E100" s="3">
         <v>506000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4244000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2408000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2152000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1130000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7937000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>575000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6821000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-242000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13039000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4842000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7875000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3974000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6573000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9114000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8571000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4986000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15134000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2206000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6298000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1859000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1202000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2083000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7487000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2804000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E101" s="3">
         <v>365000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-653000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>277000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-57000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-83000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-508000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>35000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>162000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1721000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1566000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1159000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-291000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1721000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1566000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1159000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-291000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-204000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-650000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>209000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-538000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>679000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>499000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>55000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-439000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>831000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1151000</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1985000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-509000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2787000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2991000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2413000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3007000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>172000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2461000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2429000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1623000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2532000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-841000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2413000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5041000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2915000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3093000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1572000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9934000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7629000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>328000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1642000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-983000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>675000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>866000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8093000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5718000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-102000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>731000</v>
       </c>
     </row>
